--- a/forest_monster_cards.xlsx
+++ b/forest_monster_cards.xlsx
@@ -33,7 +33,7 @@
     <t>Slash</t>
   </si>
   <si>
-    <t xml:space="preserve">Deal 1 Damage to each Adventurer.</t>
+    <t xml:space="preserve">Deal 2 Damage to each Adventurer.</t>
   </si>
   <si>
     <t>cardimages/poison_mushrooms.png</t>
@@ -42,7 +42,7 @@
     <t xml:space="preserve">Poison Mushrooms</t>
   </si>
   <si>
-    <t xml:space="preserve">Place this card face up below the monster track; next turn deal 2 damage to each Adventurer.</t>
+    <t xml:space="preserve">Place this card face up below the monster track; next turn deal 4 damage to each Adventurer.</t>
   </si>
   <si>
     <t>cardimages/tree_cover.png</t>
@@ -51,7 +51,7 @@
     <t xml:space="preserve">Tree Cover</t>
   </si>
   <si>
-    <t xml:space="preserve">Prevent 1 Damage for each Adventurer in the party.</t>
+    <t xml:space="preserve">Prevent 2 Damage for each Adventurer in the party.</t>
   </si>
   <si>
     <t>cardimages/rampant_growth.png</t>
@@ -78,7 +78,7 @@
     <t xml:space="preserve">Flash Flood</t>
   </si>
   <si>
-    <t xml:space="preserve">Deal X‑3 Damage to each Adventurer, where X is the number of cards they have in hand.</t>
+    <t xml:space="preserve">Deal X Damage to each Adventurer, where X is the number of cards they have in hand.</t>
   </si>
   <si>
     <t>cardimages/forest_maze.png</t>
@@ -105,7 +105,7 @@
     <t xml:space="preserve">Forest Fire</t>
   </si>
   <si>
-    <t xml:space="preserve">Deal 1 Unpreventable Damage to each Adventurer.</t>
+    <t xml:space="preserve">Deal 2 Unpreventable Damage to each Adventurer.</t>
   </si>
   <si>
     <t>cardimages/flowery_clearing.png</t>
